--- a/DateBase/orders/Nha Thu_2026-8-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-24.xlsx
@@ -607,6 +607,9 @@
       <c r="C21" t="str">
         <v>334_狗尾草_puppy tail grass_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -665,7 +668,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>012651075151051020101055101530150</v>
+        <v>012651075151051020101055101530155</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -611,9 +611,154 @@
         <v>5</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>451_景天_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>779_景天绿_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>592_进口春兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>816_山里红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>322_喷泉草_Grasses Panicum_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>4</v>
+      </c>
+      <c r="C29" t="str">
+        <v>635_干花安娜白_undefined_undefined_1stem</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>5</v>
+      </c>
+      <c r="C30" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>875_九星叶红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>7_翠绿洋桔梗_Dark Green Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L38"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -668,7 +813,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>012651075151051020101055101530155</v>
+        <v>0126510751510510201010551015301551055520104010555101010301510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-24.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-24.xlsx
@@ -815,6 +815,9 @@
       <c r="G2" t="str">
         <v>0126510751510510201010551015301551055520104010555101010301510</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
